--- a/Birthdays.xlsx
+++ b/Birthdays.xlsx
@@ -3241,7 +3241,7 @@
         <v>17</v>
       </c>
       <c r="E37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -4583,7 +4583,7 @@
         </is>
       </c>
       <c r="E37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">

--- a/Birthdays.xlsx
+++ b/Birthdays.xlsx
@@ -3241,7 +3241,7 @@
         <v>17</v>
       </c>
       <c r="E37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -4583,7 +4583,7 @@
         </is>
       </c>
       <c r="E37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">

--- a/Birthdays.xlsx
+++ b/Birthdays.xlsx
@@ -3264,7 +3264,7 @@
         <v>21</v>
       </c>
       <c r="E38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -4606,7 +4606,7 @@
         </is>
       </c>
       <c r="E38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">

--- a/Birthdays.xlsx
+++ b/Birthdays.xlsx
@@ -3264,7 +3264,7 @@
         <v>21</v>
       </c>
       <c r="E38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -4606,7 +4606,7 @@
         </is>
       </c>
       <c r="E38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">

--- a/Birthdays.xlsx
+++ b/Birthdays.xlsx
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="E39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -4629,7 +4629,7 @@
         </is>
       </c>
       <c r="E39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">

--- a/Birthdays.xlsx
+++ b/Birthdays.xlsx
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="E39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -4629,7 +4629,7 @@
         </is>
       </c>
       <c r="E39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">

--- a/Birthdays.xlsx
+++ b/Birthdays.xlsx
@@ -12,8 +12,8 @@
     <sheet name="Duplicate_Check" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Birthday_View'!$A$1:$E$57</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Birthday_Calendar'!$A$1:$E$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Birthday_View'!$A$1:$E$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Birthday_Calendar'!$A$1:$E$59</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Duplicate_Check'!$A$1:$E$4</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1082,7 +1082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D63"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
     <col width="17.1818181818182" customWidth="1" min="1" max="1"/>
@@ -2365,6 +2365,50 @@
       <c r="D63" t="inlineStr">
         <is>
           <t>8/20/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>10/1/2026 11:13:56</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>9/30/1986</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Pulak Sharma</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>9/30/1986</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>10/1/2026 11:14:20</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>10/1/1986</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Sudhir Bais</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>10/1/2026</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3293,21 +3337,21 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Swati Aggarwal(Bishnoi)🙂</t>
+          <t>Pulak Sharma</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>10/1/1987</t>
+          <t>9/30/1986</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>October</t>
+          <t>September</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E40" t="b">
         <v>0</v>
@@ -3316,12 +3360,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Jaspreet</t>
+          <t>Sudhir Bais</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>10/5/2026</t>
+          <t>10/1/1986</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3330,21 +3374,21 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Jaspreet Sethi</t>
+          <t>Swati Aggarwal(Bishnoi)🙂</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>10/5/1987</t>
+          <t>10/1/1987</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3353,21 +3397,21 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Priyanka Verma</t>
+          <t>Jaspreet</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>10/18/1987</t>
+          <t>10/5/2026</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3376,7 +3420,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E43" t="b">
         <v>0</v>
@@ -3385,12 +3429,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Bhumika chaudhary</t>
+          <t>Jaspreet Sethi</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>10/28/1988</t>
+          <t>10/5/1987</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3399,7 +3443,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="E44" t="b">
         <v>0</v>
@@ -3408,12 +3452,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Nimesh</t>
+          <t>Priyanka Verma</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>10/30/1987</t>
+          <t>10/18/1987</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3422,7 +3466,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E45" t="b">
         <v>0</v>
@@ -3431,21 +3475,21 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Shobhit kaushik</t>
+          <t>Bhumika chaudhary</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>11/13/1986</t>
+          <t>10/28/1988</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>November</t>
+          <t>October</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E46" t="b">
         <v>0</v>
@@ -3454,21 +3498,21 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Pratyaksh Tomar</t>
+          <t>Nimesh</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>11/28/2026</t>
+          <t>10/30/1987</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>November</t>
+          <t>October</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E47" t="b">
         <v>0</v>
@@ -3477,12 +3521,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SUMIT CHHABRA</t>
+          <t>Shobhit kaushik</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>11/28/1987</t>
+          <t>11/13/1986</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,7 +3535,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E48" t="b">
         <v>0</v>
@@ -3500,21 +3544,21 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Ishan Bhardwaj</t>
+          <t>Pratyaksh Tomar</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>12/4/2026</t>
+          <t>11/28/2026</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>December</t>
+          <t>November</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="E49" t="b">
         <v>0</v>
@@ -3523,21 +3567,21 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Ishan Bhardwaj</t>
+          <t>SUMIT CHHABRA</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>12/4/1986</t>
+          <t>11/28/1987</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>December</t>
+          <t>November</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="E50" t="b">
         <v>0</v>
@@ -3546,12 +3590,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Isha shukla</t>
+          <t>Ishan Bhardwaj</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>12/6/0086</t>
+          <t>12/4/2026</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3560,7 +3604,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E51" t="b">
         <v>0</v>
@@ -3569,12 +3613,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Kriti Sharma</t>
+          <t>Ishan Bhardwaj</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>12/7/1988</t>
+          <t>12/4/1986</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3583,7 +3627,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E52" t="b">
         <v>0</v>
@@ -3592,12 +3636,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Shashank Chaudhary</t>
+          <t>Isha shukla</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>12/10/1987</t>
+          <t>12/6/0086</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3606,7 +3650,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E53" t="b">
         <v>0</v>
@@ -3615,12 +3659,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Gopal Verma</t>
+          <t>Kriti Sharma</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>12/17/1987</t>
+          <t>12/7/1988</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3629,7 +3673,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E54" t="b">
         <v>0</v>
@@ -3638,12 +3682,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SEERAT KAUR (FORMERLY SUMIT KAPOOR)</t>
+          <t>Shashank Chaudhary</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>12/18/1987</t>
+          <t>12/10/1987</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3652,7 +3696,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E55" t="b">
         <v>0</v>
@@ -3661,12 +3705,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Prasanjeet</t>
+          <t>Gopal Verma</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>12/28/1986</t>
+          <t>12/17/1987</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3675,7 +3719,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E56" t="b">
         <v>0</v>
@@ -3684,29 +3728,75 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>SEERAT KAUR (FORMERLY SUMIT KAPOOR)</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>12/18/1987</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>December</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>18</v>
+      </c>
+      <c r="E57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Prasanjeet</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>12/28/1986</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>December</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>28</v>
+      </c>
+      <c r="E58" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>Ashu Garg</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>12/29/1986</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>December</t>
         </is>
       </c>
-      <c r="D57" t="n">
+      <c r="D59" t="n">
         <v>29</v>
       </c>
-      <c r="E57" t="b">
+      <c r="E59" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E57"/>
-  <conditionalFormatting sqref="A2:E57">
+  <autoFilter ref="A1:E59"/>
+  <conditionalFormatting sqref="A2:E59">
     <cfRule type="expression" priority="1" dxfId="1">
       <formula>$E2=TRUE</formula>
     </cfRule>
@@ -3721,7 +3811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4635,20 +4725,20 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>October</t>
+          <t>September</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Swati Aggarwal(Bishnoi)🙂</t>
+          <t>Pulak Sharma</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>10/1/1987</t>
+          <t>9/30/1986</t>
         </is>
       </c>
       <c r="E40" t="b">
@@ -4662,20 +4752,20 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jaspreet</t>
+          <t>Sudhir Bais</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>10/5/2026</t>
+          <t>10/1/1986</t>
         </is>
       </c>
       <c r="E41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -4685,20 +4775,20 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Jaspreet Sethi</t>
+          <t>Swati Aggarwal(Bishnoi)🙂</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>10/5/1987</t>
+          <t>10/1/1987</t>
         </is>
       </c>
       <c r="E42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -4708,16 +4798,16 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Priyanka Verma</t>
+          <t>Jaspreet</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>10/18/1987</t>
+          <t>10/5/2026</t>
         </is>
       </c>
       <c r="E43" t="b">
@@ -4731,16 +4821,16 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bhumika chaudhary</t>
+          <t>Jaspreet Sethi</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>10/28/1988</t>
+          <t>10/5/1987</t>
         </is>
       </c>
       <c r="E44" t="b">
@@ -4754,16 +4844,16 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Nimesh</t>
+          <t>Priyanka Verma</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>10/30/1987</t>
+          <t>10/18/1987</t>
         </is>
       </c>
       <c r="E45" t="b">
@@ -4773,20 +4863,20 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>November</t>
+          <t>October</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Shobhit kaushik</t>
+          <t>Bhumika chaudhary</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>11/13/1986</t>
+          <t>10/28/1988</t>
         </is>
       </c>
       <c r="E46" t="b">
@@ -4796,20 +4886,20 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>November</t>
+          <t>October</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Pratyaksh Tomar</t>
+          <t>Nimesh</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>11/28/2026</t>
+          <t>10/30/1987</t>
         </is>
       </c>
       <c r="E47" t="b">
@@ -4823,16 +4913,16 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SUMIT CHHABRA</t>
+          <t>Shobhit kaushik</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>11/28/1987</t>
+          <t>11/13/1986</t>
         </is>
       </c>
       <c r="E48" t="b">
@@ -4842,20 +4932,20 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>December</t>
+          <t>November</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ishan Bhardwaj</t>
+          <t>Pratyaksh Tomar</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>12/4/2026</t>
+          <t>11/28/2026</t>
         </is>
       </c>
       <c r="E49" t="b">
@@ -4865,20 +4955,20 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>December</t>
+          <t>November</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ishan Bhardwaj</t>
+          <t>SUMIT CHHABRA</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>12/4/1986</t>
+          <t>11/28/1987</t>
         </is>
       </c>
       <c r="E50" t="b">
@@ -4892,16 +4982,16 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Isha shukla</t>
+          <t>Ishan Bhardwaj</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>12/6/0086</t>
+          <t>12/4/2026</t>
         </is>
       </c>
       <c r="E51" t="b">
@@ -4915,16 +5005,16 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Kriti Sharma</t>
+          <t>Ishan Bhardwaj</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>12/7/1988</t>
+          <t>12/4/1986</t>
         </is>
       </c>
       <c r="E52" t="b">
@@ -4938,16 +5028,16 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Shashank Chaudhary</t>
+          <t>Isha shukla</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>12/10/1987</t>
+          <t>12/6/0086</t>
         </is>
       </c>
       <c r="E53" t="b">
@@ -4961,16 +5051,16 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Gopal Verma</t>
+          <t>Kriti Sharma</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>12/17/1987</t>
+          <t>12/7/1988</t>
         </is>
       </c>
       <c r="E54" t="b">
@@ -4984,16 +5074,16 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SEERAT KAUR (FORMERLY SUMIT KAPOOR)</t>
+          <t>Shashank Chaudhary</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>12/18/1987</t>
+          <t>12/10/1987</t>
         </is>
       </c>
       <c r="E55" t="b">
@@ -5007,16 +5097,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Prasanjeet</t>
+          <t>Gopal Verma</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>12/28/1986</t>
+          <t>12/17/1987</t>
         </is>
       </c>
       <c r="E56" t="b">
@@ -5030,25 +5120,71 @@
         </is>
       </c>
       <c r="B57" t="n">
+        <v>18</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>SEERAT KAUR (FORMERLY SUMIT KAPOOR)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>12/18/1987</t>
+        </is>
+      </c>
+      <c r="E57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>December</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>28</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Prasanjeet</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>12/28/1986</t>
+        </is>
+      </c>
+      <c r="E58" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>December</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
         <v>29</v>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Ashu Garg</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>12/29/1986</t>
         </is>
       </c>
-      <c r="E57" t="b">
+      <c r="E59" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E57"/>
-  <conditionalFormatting sqref="A2:E57">
+  <autoFilter ref="A1:E59"/>
+  <conditionalFormatting sqref="A2:E59">
     <cfRule type="expression" priority="1" dxfId="1">
       <formula>$E2=TRUE</formula>
     </cfRule>

--- a/Birthdays.xlsx
+++ b/Birthdays.xlsx
@@ -12,8 +12,8 @@
     <sheet name="Duplicate_Check" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Birthday_View'!$A$1:$E$59</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Birthday_Calendar'!$A$1:$E$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Birthday_View'!$A$1:$E$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Birthday_Calendar'!$A$1:$E$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Duplicate_Check'!$A$1:$E$4</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1082,7 +1082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D65"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
     <col width="17.1818181818182" customWidth="1" min="1" max="1"/>
@@ -2409,6 +2409,50 @@
       <c r="D65" t="inlineStr">
         <is>
           <t>10/1/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>10/2/2026 11:20:33</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>10/2/1986</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Pramod</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>10/2/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>10/2/2026 11:53:23</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>12/14/1989</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Pallavi Sharma</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>10/2/2026</t>
         </is>
       </c>
     </row>
@@ -2423,7 +2467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3377,7 +3421,7 @@
         <v>1</v>
       </c>
       <c r="E41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -3400,18 +3444,18 @@
         <v>1</v>
       </c>
       <c r="E42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Jaspreet</t>
+          <t>Pramod</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>10/5/2026</t>
+          <t>10/2/1986</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3420,21 +3464,21 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Jaspreet Sethi</t>
+          <t>Jaspreet</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>10/5/1987</t>
+          <t>10/5/2026</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3452,12 +3496,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Priyanka Verma</t>
+          <t>Jaspreet Sethi</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>10/18/1987</t>
+          <t>10/5/1987</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3466,7 +3510,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E45" t="b">
         <v>0</v>
@@ -3475,12 +3519,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Bhumika chaudhary</t>
+          <t>Priyanka Verma</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>10/28/1988</t>
+          <t>10/18/1987</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3489,7 +3533,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E46" t="b">
         <v>0</v>
@@ -3498,12 +3542,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Nimesh</t>
+          <t>Bhumika chaudhary</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>10/30/1987</t>
+          <t>10/28/1988</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3512,7 +3556,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E47" t="b">
         <v>0</v>
@@ -3521,21 +3565,21 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Shobhit kaushik</t>
+          <t>Nimesh</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>11/13/1986</t>
+          <t>10/30/1987</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>November</t>
+          <t>October</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E48" t="b">
         <v>0</v>
@@ -3544,12 +3588,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Pratyaksh Tomar</t>
+          <t>Shobhit kaushik</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>11/28/2026</t>
+          <t>11/13/1986</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3558,7 +3602,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E49" t="b">
         <v>0</v>
@@ -3567,12 +3611,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SUMIT CHHABRA</t>
+          <t>Pratyaksh Tomar</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>11/28/1987</t>
+          <t>11/28/2026</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3590,21 +3634,21 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Ishan Bhardwaj</t>
+          <t>SUMIT CHHABRA</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>12/4/2026</t>
+          <t>11/28/1987</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>December</t>
+          <t>November</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="E51" t="b">
         <v>0</v>
@@ -3618,7 +3662,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>12/4/1986</t>
+          <t>12/4/2026</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3636,12 +3680,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Isha shukla</t>
+          <t>Ishan Bhardwaj</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>12/6/0086</t>
+          <t>12/4/1986</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3650,7 +3694,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E53" t="b">
         <v>0</v>
@@ -3659,12 +3703,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Kriti Sharma</t>
+          <t>Isha shukla</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>12/7/1988</t>
+          <t>12/6/0086</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3673,7 +3717,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E54" t="b">
         <v>0</v>
@@ -3682,12 +3726,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Shashank Chaudhary</t>
+          <t>Kriti Sharma</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>12/10/1987</t>
+          <t>12/7/1988</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3696,7 +3740,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E55" t="b">
         <v>0</v>
@@ -3705,12 +3749,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Gopal Verma</t>
+          <t>Shashank Chaudhary</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>12/17/1987</t>
+          <t>12/10/1987</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3719,7 +3763,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E56" t="b">
         <v>0</v>
@@ -3728,12 +3772,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SEERAT KAUR (FORMERLY SUMIT KAPOOR)</t>
+          <t>Pallavi Sharma</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>12/18/1987</t>
+          <t>12/14/1989</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3742,7 +3786,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E57" t="b">
         <v>0</v>
@@ -3751,12 +3795,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Prasanjeet</t>
+          <t>Gopal Verma</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>12/28/1986</t>
+          <t>12/17/1987</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3765,7 +3809,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E58" t="b">
         <v>0</v>
@@ -3774,29 +3818,75 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>SEERAT KAUR (FORMERLY SUMIT KAPOOR)</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>12/18/1987</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>December</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>18</v>
+      </c>
+      <c r="E59" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Prasanjeet</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>12/28/1986</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>December</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>28</v>
+      </c>
+      <c r="E60" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
           <t>Ashu Garg</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>12/29/1986</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>December</t>
         </is>
       </c>
-      <c r="D59" t="n">
+      <c r="D61" t="n">
         <v>29</v>
       </c>
-      <c r="E59" t="b">
+      <c r="E61" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E59"/>
-  <conditionalFormatting sqref="A2:E59">
+  <autoFilter ref="A1:E61"/>
+  <conditionalFormatting sqref="A2:E61">
     <cfRule type="expression" priority="1" dxfId="1">
       <formula>$E2=TRUE</formula>
     </cfRule>
@@ -3811,7 +3901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4765,7 +4855,7 @@
         </is>
       </c>
       <c r="E41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -4788,7 +4878,7 @@
         </is>
       </c>
       <c r="E42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -4798,20 +4888,20 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Jaspreet</t>
+          <t>Pramod</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>10/5/2026</t>
+          <t>10/2/1986</t>
         </is>
       </c>
       <c r="E43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -4825,12 +4915,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jaspreet Sethi</t>
+          <t>Jaspreet</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>10/5/1987</t>
+          <t>10/5/2026</t>
         </is>
       </c>
       <c r="E44" t="b">
@@ -4844,16 +4934,16 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Priyanka Verma</t>
+          <t>Jaspreet Sethi</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>10/18/1987</t>
+          <t>10/5/1987</t>
         </is>
       </c>
       <c r="E45" t="b">
@@ -4867,16 +4957,16 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bhumika chaudhary</t>
+          <t>Priyanka Verma</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>10/28/1988</t>
+          <t>10/18/1987</t>
         </is>
       </c>
       <c r="E46" t="b">
@@ -4890,16 +4980,16 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Nimesh</t>
+          <t>Bhumika chaudhary</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>10/30/1987</t>
+          <t>10/28/1988</t>
         </is>
       </c>
       <c r="E47" t="b">
@@ -4909,20 +4999,20 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>November</t>
+          <t>October</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Shobhit kaushik</t>
+          <t>Nimesh</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>11/13/1986</t>
+          <t>10/30/1987</t>
         </is>
       </c>
       <c r="E48" t="b">
@@ -4936,16 +5026,16 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Pratyaksh Tomar</t>
+          <t>Shobhit kaushik</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>11/28/2026</t>
+          <t>11/13/1986</t>
         </is>
       </c>
       <c r="E49" t="b">
@@ -4963,12 +5053,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SUMIT CHHABRA</t>
+          <t>Pratyaksh Tomar</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>11/28/1987</t>
+          <t>11/28/2026</t>
         </is>
       </c>
       <c r="E50" t="b">
@@ -4978,20 +5068,20 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>December</t>
+          <t>November</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ishan Bhardwaj</t>
+          <t>SUMIT CHHABRA</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>12/4/2026</t>
+          <t>11/28/1987</t>
         </is>
       </c>
       <c r="E51" t="b">
@@ -5014,7 +5104,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>12/4/1986</t>
+          <t>12/4/2026</t>
         </is>
       </c>
       <c r="E52" t="b">
@@ -5028,16 +5118,16 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Isha shukla</t>
+          <t>Ishan Bhardwaj</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>12/6/0086</t>
+          <t>12/4/1986</t>
         </is>
       </c>
       <c r="E53" t="b">
@@ -5051,16 +5141,16 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Kriti Sharma</t>
+          <t>Isha shukla</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>12/7/1988</t>
+          <t>12/6/0086</t>
         </is>
       </c>
       <c r="E54" t="b">
@@ -5074,16 +5164,16 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Shashank Chaudhary</t>
+          <t>Kriti Sharma</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>12/10/1987</t>
+          <t>12/7/1988</t>
         </is>
       </c>
       <c r="E55" t="b">
@@ -5097,16 +5187,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Gopal Verma</t>
+          <t>Shashank Chaudhary</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>12/17/1987</t>
+          <t>12/10/1987</t>
         </is>
       </c>
       <c r="E56" t="b">
@@ -5120,16 +5210,16 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SEERAT KAUR (FORMERLY SUMIT KAPOOR)</t>
+          <t>Pallavi Sharma</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>12/18/1987</t>
+          <t>12/14/1989</t>
         </is>
       </c>
       <c r="E57" t="b">
@@ -5143,16 +5233,16 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Prasanjeet</t>
+          <t>Gopal Verma</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>12/28/1986</t>
+          <t>12/17/1987</t>
         </is>
       </c>
       <c r="E58" t="b">
@@ -5166,25 +5256,71 @@
         </is>
       </c>
       <c r="B59" t="n">
+        <v>18</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>SEERAT KAUR (FORMERLY SUMIT KAPOOR)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>12/18/1987</t>
+        </is>
+      </c>
+      <c r="E59" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>December</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>28</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Prasanjeet</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>12/28/1986</t>
+        </is>
+      </c>
+      <c r="E60" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>December</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
         <v>29</v>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>Ashu Garg</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>12/29/1986</t>
         </is>
       </c>
-      <c r="E59" t="b">
+      <c r="E61" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E59"/>
-  <conditionalFormatting sqref="A2:E59">
+  <autoFilter ref="A1:E61"/>
+  <conditionalFormatting sqref="A2:E61">
     <cfRule type="expression" priority="1" dxfId="1">
       <formula>$E2=TRUE</formula>
     </cfRule>

--- a/Birthdays.xlsx
+++ b/Birthdays.xlsx
@@ -3467,7 +3467,7 @@
         <v>2</v>
       </c>
       <c r="E43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -4901,7 +4901,7 @@
         </is>
       </c>
       <c r="E43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">

--- a/Birthdays.xlsx
+++ b/Birthdays.xlsx
@@ -3490,7 +3490,7 @@
         <v>5</v>
       </c>
       <c r="E44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -3513,7 +3513,7 @@
         <v>5</v>
       </c>
       <c r="E45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -4924,7 +4924,7 @@
         </is>
       </c>
       <c r="E44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="E45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">

--- a/Birthdays.xlsx
+++ b/Birthdays.xlsx
@@ -3490,7 +3490,7 @@
         <v>5</v>
       </c>
       <c r="E44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -3513,7 +3513,7 @@
         <v>5</v>
       </c>
       <c r="E45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -4924,7 +4924,7 @@
         </is>
       </c>
       <c r="E44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="E45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">

--- a/Birthdays.xlsx
+++ b/Birthdays.xlsx
@@ -12,8 +12,8 @@
     <sheet name="Duplicate_Check" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Birthday_View'!$A$1:$E$61</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Birthday_Calendar'!$A$1:$E$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Birthday_View'!$A$1:$E$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Birthday_Calendar'!$A$1:$E$62</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Duplicate_Check'!$A$1:$E$4</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1082,7 +1082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D67"/>
+  <dimension ref="A1:D68"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
     <col width="17.1818181818182" customWidth="1" min="1" max="1"/>
@@ -2453,6 +2453,28 @@
       <c r="D67" t="inlineStr">
         <is>
           <t>10/2/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>10/18/2026 11:51:55</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>3/3/1987</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Chanchal</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>10/18/2026</t>
         </is>
       </c>
     </row>
@@ -2467,7 +2489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2737,21 +2759,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mohit sharma</t>
+          <t>Chanchal</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4/11/1987</t>
+          <t>3/3/1987</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>April</t>
+          <t>March</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
@@ -2760,12 +2782,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Chetan</t>
+          <t>Mohit sharma</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4/16/1988</t>
+          <t>4/11/1987</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2774,7 +2796,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
@@ -2783,12 +2805,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Tanuj Sablok</t>
+          <t>Chetan</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4/16/1987</t>
+          <t>4/16/1988</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2806,12 +2828,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Atul Sharma</t>
+          <t>Tanuj Sablok</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4/22/1987</t>
+          <t>4/16/1987</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2820,7 +2842,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
@@ -2829,21 +2851,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Mayank Gambhir</t>
+          <t>Atul Sharma</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5/7/1988</t>
+          <t>4/22/1987</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>April</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
@@ -2852,12 +2874,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MUKUL</t>
+          <t>Mayank Gambhir</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5/17/2026</t>
+          <t>5/7/1988</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2866,7 +2888,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E17" t="b">
         <v>0</v>
@@ -2875,12 +2897,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>mukul</t>
+          <t>MUKUL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5/17/1988</t>
+          <t>5/17/2026</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2898,21 +2920,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ashish tyagi</t>
+          <t>mukul</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>7/8/2026</t>
+          <t>5/17/1988</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
@@ -2926,7 +2948,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7/8/1988</t>
+          <t>7/8/2026</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2944,12 +2966,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ayush manglik</t>
+          <t>Ashish tyagi</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>7/9/1987</t>
+          <t>7/8/1988</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2958,7 +2980,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E21" t="b">
         <v>0</v>
@@ -2967,12 +2989,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Kavita Babbar</t>
+          <t>Ayush manglik</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>7/10/1987</t>
+          <t>7/9/1987</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2981,7 +3003,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E22" t="b">
         <v>0</v>
@@ -2990,12 +3012,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Pallavi Tomar</t>
+          <t>Kavita Babbar</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>7/20/1987</t>
+          <t>7/10/1987</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3004,7 +3026,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E23" t="b">
         <v>0</v>
@@ -3013,12 +3035,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rekha</t>
+          <t>Pallavi Tomar</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>7/21/2026</t>
+          <t>7/20/1987</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3027,7 +3049,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E24" t="b">
         <v>0</v>
@@ -3036,12 +3058,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rekha Lakchaura</t>
+          <t>Rekha</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>7/21/1988</t>
+          <t>7/21/2026</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3059,12 +3081,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Jatin</t>
+          <t>Rekha Lakchaura</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>7/28/1988</t>
+          <t>7/21/1988</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3073,7 +3095,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E26" t="b">
         <v>0</v>
@@ -3082,21 +3104,21 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Shatakshi Verma</t>
+          <t>Jatin</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>8/4/1987</t>
+          <t>7/28/1988</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>July</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="E27" t="b">
         <v>0</v>
@@ -3105,12 +3127,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Swati Tyagi</t>
+          <t>Shatakshi Verma</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>8/5/1988</t>
+          <t>8/4/1987</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3119,7 +3141,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E28" t="b">
         <v>0</v>
@@ -3128,7 +3150,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Xyz</t>
+          <t>Swati Tyagi</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3151,12 +3173,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Dhirendra</t>
+          <t>Xyz</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>8/7/1988</t>
+          <t>8/5/1988</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3165,7 +3187,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E30" t="b">
         <v>0</v>
@@ -3174,7 +3196,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Harsh Dutt</t>
+          <t>Dhirendra</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3197,12 +3219,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Rohit Pradhan</t>
+          <t>Harsh Dutt</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>8/8/1988</t>
+          <t>8/7/1988</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3211,7 +3233,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E32" t="b">
         <v>0</v>
@@ -3220,12 +3242,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Vivek Ahlawat</t>
+          <t>Rohit Pradhan</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>8/14/1988</t>
+          <t>8/8/1988</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3234,7 +3256,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E33" t="b">
         <v>0</v>
@@ -3243,12 +3265,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Vibhor Agarwal</t>
+          <t>Vivek Ahlawat</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>8/19/0087</t>
+          <t>8/14/1988</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3257,7 +3279,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E34" t="b">
         <v>0</v>
@@ -3266,12 +3288,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Lavi Aggarwal</t>
+          <t>Vibhor Agarwal</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>8/25/1987</t>
+          <t>8/19/0087</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3280,7 +3302,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E35" t="b">
         <v>0</v>
@@ -3289,12 +3311,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Ajeet Singh</t>
+          <t>Lavi Aggarwal</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>8/31/1987</t>
+          <t>8/25/1987</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3303,7 +3325,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E36" t="b">
         <v>0</v>
@@ -3312,21 +3334,21 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sakshi Goel Agarwal</t>
+          <t>Ajeet Singh</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>9/17/1988</t>
+          <t>8/31/1987</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>September</t>
+          <t>August</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="E37" t="b">
         <v>0</v>
@@ -3335,12 +3357,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Richa Sharma</t>
+          <t>Sakshi Goel Agarwal</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>9/21/2026</t>
+          <t>9/17/1988</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3349,7 +3371,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E38" t="b">
         <v>0</v>
@@ -3358,12 +3380,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Raavi</t>
+          <t>Richa Sharma</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>9/25/1988</t>
+          <t>9/21/2026</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3372,7 +3394,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E39" t="b">
         <v>0</v>
@@ -3381,12 +3403,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Pulak Sharma</t>
+          <t>Raavi</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>9/30/1986</t>
+          <t>9/25/1988</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3395,7 +3417,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E40" t="b">
         <v>0</v>
@@ -3404,21 +3426,21 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sudhir Bais</t>
+          <t>Pulak Sharma</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>10/1/1986</t>
+          <t>9/30/1986</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>October</t>
+          <t>September</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E41" t="b">
         <v>0</v>
@@ -3427,12 +3449,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Swati Aggarwal(Bishnoi)🙂</t>
+          <t>Sudhir Bais</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>10/1/1987</t>
+          <t>10/1/1986</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3450,12 +3472,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Pramod</t>
+          <t>Swati Aggarwal(Bishnoi)🙂</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>10/2/1986</t>
+          <t>10/1/1987</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3464,7 +3486,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E43" t="b">
         <v>0</v>
@@ -3473,12 +3495,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Jaspreet</t>
+          <t>Pramod</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>10/5/2026</t>
+          <t>10/2/1986</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3487,7 +3509,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E44" t="b">
         <v>0</v>
@@ -3496,12 +3518,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Jaspreet Sethi</t>
+          <t>Jaspreet</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>10/5/1987</t>
+          <t>10/5/2026</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3519,12 +3541,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Priyanka Verma</t>
+          <t>Jaspreet Sethi</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>10/18/1987</t>
+          <t>10/5/1987</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3533,7 +3555,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E46" t="b">
         <v>0</v>
@@ -3542,12 +3564,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Bhumika chaudhary</t>
+          <t>Priyanka Verma</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>10/28/1988</t>
+          <t>10/18/1987</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3556,21 +3578,21 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Nimesh</t>
+          <t>Bhumika chaudhary</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>10/30/1987</t>
+          <t>10/28/1988</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3579,7 +3601,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E48" t="b">
         <v>0</v>
@@ -3588,21 +3610,21 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Shobhit kaushik</t>
+          <t>Nimesh</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>11/13/1986</t>
+          <t>10/30/1987</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>November</t>
+          <t>October</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E49" t="b">
         <v>0</v>
@@ -3611,12 +3633,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Pratyaksh Tomar</t>
+          <t>Shobhit kaushik</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>11/28/2026</t>
+          <t>11/13/1986</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3625,7 +3647,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E50" t="b">
         <v>0</v>
@@ -3634,12 +3656,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SUMIT CHHABRA</t>
+          <t>Pratyaksh Tomar</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>11/28/1987</t>
+          <t>11/28/2026</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3657,21 +3679,21 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Ishan Bhardwaj</t>
+          <t>SUMIT CHHABRA</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>12/4/2026</t>
+          <t>11/28/1987</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>December</t>
+          <t>November</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="E52" t="b">
         <v>0</v>
@@ -3685,7 +3707,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>12/4/1986</t>
+          <t>12/4/2026</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3703,12 +3725,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Isha shukla</t>
+          <t>Ishan Bhardwaj</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>12/6/0086</t>
+          <t>12/4/1986</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3717,7 +3739,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E54" t="b">
         <v>0</v>
@@ -3726,12 +3748,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Kriti Sharma</t>
+          <t>Isha shukla</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>12/7/1988</t>
+          <t>12/6/0086</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3740,7 +3762,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E55" t="b">
         <v>0</v>
@@ -3749,12 +3771,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Shashank Chaudhary</t>
+          <t>Kriti Sharma</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>12/10/1987</t>
+          <t>12/7/1988</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3763,7 +3785,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E56" t="b">
         <v>0</v>
@@ -3772,12 +3794,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Pallavi Sharma</t>
+          <t>Shashank Chaudhary</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>12/14/1989</t>
+          <t>12/10/1987</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3786,7 +3808,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E57" t="b">
         <v>0</v>
@@ -3795,12 +3817,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Gopal Verma</t>
+          <t>Pallavi Sharma</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>12/17/1987</t>
+          <t>12/14/1989</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3809,7 +3831,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E58" t="b">
         <v>0</v>
@@ -3818,12 +3840,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SEERAT KAUR (FORMERLY SUMIT KAPOOR)</t>
+          <t>Gopal Verma</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>12/18/1987</t>
+          <t>12/17/1987</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3832,7 +3854,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E59" t="b">
         <v>0</v>
@@ -3841,12 +3863,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Prasanjeet</t>
+          <t>SEERAT KAUR (FORMERLY SUMIT KAPOOR)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>12/28/1986</t>
+          <t>12/18/1987</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3855,7 +3877,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E60" t="b">
         <v>0</v>
@@ -3864,29 +3886,52 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>Prasanjeet</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>12/28/1986</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>December</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>28</v>
+      </c>
+      <c r="E61" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
           <t>Ashu Garg</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>12/29/1986</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>December</t>
         </is>
       </c>
-      <c r="D61" t="n">
+      <c r="D62" t="n">
         <v>29</v>
       </c>
-      <c r="E61" t="b">
+      <c r="E62" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E61"/>
-  <conditionalFormatting sqref="A2:E61">
+  <autoFilter ref="A1:E62"/>
+  <conditionalFormatting sqref="A2:E62">
     <cfRule type="expression" priority="1" dxfId="1">
       <formula>$E2=TRUE</formula>
     </cfRule>
@@ -3901,7 +3946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4171,20 +4216,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>April</t>
+          <t>March</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mohit sharma</t>
+          <t>Chanchal</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4/11/1987</t>
+          <t>3/3/1987</t>
         </is>
       </c>
       <c r="E12" t="b">
@@ -4198,16 +4243,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chetan</t>
+          <t>Mohit sharma</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4/16/1988</t>
+          <t>4/11/1987</t>
         </is>
       </c>
       <c r="E13" t="b">
@@ -4225,12 +4270,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tanuj Sablok</t>
+          <t>Chetan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4/16/1987</t>
+          <t>4/16/1988</t>
         </is>
       </c>
       <c r="E14" t="b">
@@ -4244,16 +4289,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Atul Sharma</t>
+          <t>Tanuj Sablok</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4/22/1987</t>
+          <t>4/16/1987</t>
         </is>
       </c>
       <c r="E15" t="b">
@@ -4263,20 +4308,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>April</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mayank Gambhir</t>
+          <t>Atul Sharma</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>5/7/1988</t>
+          <t>4/22/1987</t>
         </is>
       </c>
       <c r="E16" t="b">
@@ -4290,16 +4335,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MUKUL</t>
+          <t>Mayank Gambhir</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>5/17/2026</t>
+          <t>5/7/1988</t>
         </is>
       </c>
       <c r="E17" t="b">
@@ -4317,12 +4362,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>mukul</t>
+          <t>MUKUL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>5/17/1988</t>
+          <t>5/17/2026</t>
         </is>
       </c>
       <c r="E18" t="b">
@@ -4332,20 +4377,20 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>May</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ashish tyagi</t>
+          <t>mukul</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>7/8/2026</t>
+          <t>5/17/1988</t>
         </is>
       </c>
       <c r="E19" t="b">
@@ -4368,7 +4413,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>7/8/1988</t>
+          <t>7/8/2026</t>
         </is>
       </c>
       <c r="E20" t="b">
@@ -4382,16 +4427,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ayush manglik</t>
+          <t>Ashish tyagi</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>7/9/1987</t>
+          <t>7/8/1988</t>
         </is>
       </c>
       <c r="E21" t="b">
@@ -4405,16 +4450,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kavita Babbar</t>
+          <t>Ayush manglik</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>7/10/1987</t>
+          <t>7/9/1987</t>
         </is>
       </c>
       <c r="E22" t="b">
@@ -4428,16 +4473,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pallavi Tomar</t>
+          <t>Kavita Babbar</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>7/20/1987</t>
+          <t>7/10/1987</t>
         </is>
       </c>
       <c r="E23" t="b">
@@ -4451,16 +4496,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Rekha</t>
+          <t>Pallavi Tomar</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>7/21/2026</t>
+          <t>7/20/1987</t>
         </is>
       </c>
       <c r="E24" t="b">
@@ -4478,12 +4523,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Rekha Lakchaura</t>
+          <t>Rekha</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>7/21/1988</t>
+          <t>7/21/2026</t>
         </is>
       </c>
       <c r="E25" t="b">
@@ -4497,16 +4542,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jatin</t>
+          <t>Rekha Lakchaura</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>7/28/1988</t>
+          <t>7/21/1988</t>
         </is>
       </c>
       <c r="E26" t="b">
@@ -4516,20 +4561,20 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>July</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Shatakshi Verma</t>
+          <t>Jatin</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8/4/1987</t>
+          <t>7/28/1988</t>
         </is>
       </c>
       <c r="E27" t="b">
@@ -4543,16 +4588,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Swati Tyagi</t>
+          <t>Shatakshi Verma</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8/5/1988</t>
+          <t>8/4/1987</t>
         </is>
       </c>
       <c r="E28" t="b">
@@ -4570,7 +4615,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Xyz</t>
+          <t>Swati Tyagi</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4589,16 +4634,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dhirendra</t>
+          <t>Xyz</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8/7/1988</t>
+          <t>8/5/1988</t>
         </is>
       </c>
       <c r="E30" t="b">
@@ -4616,7 +4661,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Harsh Dutt</t>
+          <t>Dhirendra</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4635,16 +4680,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Rohit Pradhan</t>
+          <t>Harsh Dutt</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8/8/1988</t>
+          <t>8/7/1988</t>
         </is>
       </c>
       <c r="E32" t="b">
@@ -4658,16 +4703,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Vivek Ahlawat</t>
+          <t>Rohit Pradhan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8/14/1988</t>
+          <t>8/8/1988</t>
         </is>
       </c>
       <c r="E33" t="b">
@@ -4681,16 +4726,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Vibhor Agarwal</t>
+          <t>Vivek Ahlawat</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8/19/0087</t>
+          <t>8/14/1988</t>
         </is>
       </c>
       <c r="E34" t="b">
@@ -4704,16 +4749,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Lavi Aggarwal</t>
+          <t>Vibhor Agarwal</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8/25/1987</t>
+          <t>8/19/0087</t>
         </is>
       </c>
       <c r="E35" t="b">
@@ -4727,16 +4772,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ajeet Singh</t>
+          <t>Lavi Aggarwal</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8/31/1987</t>
+          <t>8/25/1987</t>
         </is>
       </c>
       <c r="E36" t="b">
@@ -4746,20 +4791,20 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>September</t>
+          <t>August</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sakshi Goel Agarwal</t>
+          <t>Ajeet Singh</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>9/17/1988</t>
+          <t>8/31/1987</t>
         </is>
       </c>
       <c r="E37" t="b">
@@ -4773,16 +4818,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Richa Sharma</t>
+          <t>Sakshi Goel Agarwal</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>9/21/2026</t>
+          <t>9/17/1988</t>
         </is>
       </c>
       <c r="E38" t="b">
@@ -4796,16 +4841,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Raavi</t>
+          <t>Richa Sharma</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>9/25/1988</t>
+          <t>9/21/2026</t>
         </is>
       </c>
       <c r="E39" t="b">
@@ -4819,16 +4864,16 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pulak Sharma</t>
+          <t>Raavi</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>9/30/1986</t>
+          <t>9/25/1988</t>
         </is>
       </c>
       <c r="E40" t="b">
@@ -4838,20 +4883,20 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>October</t>
+          <t>September</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sudhir Bais</t>
+          <t>Pulak Sharma</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>10/1/1986</t>
+          <t>9/30/1986</t>
         </is>
       </c>
       <c r="E41" t="b">
@@ -4869,12 +4914,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Swati Aggarwal(Bishnoi)🙂</t>
+          <t>Sudhir Bais</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>10/1/1987</t>
+          <t>10/1/1986</t>
         </is>
       </c>
       <c r="E42" t="b">
@@ -4888,16 +4933,16 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Pramod</t>
+          <t>Swati Aggarwal(Bishnoi)🙂</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>10/2/1986</t>
+          <t>10/1/1987</t>
         </is>
       </c>
       <c r="E43" t="b">
@@ -4911,16 +4956,16 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jaspreet</t>
+          <t>Pramod</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>10/5/2026</t>
+          <t>10/2/1986</t>
         </is>
       </c>
       <c r="E44" t="b">
@@ -4938,12 +4983,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jaspreet Sethi</t>
+          <t>Jaspreet</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>10/5/1987</t>
+          <t>10/5/2026</t>
         </is>
       </c>
       <c r="E45" t="b">
@@ -4957,16 +5002,16 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Priyanka Verma</t>
+          <t>Jaspreet Sethi</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>10/18/1987</t>
+          <t>10/5/1987</t>
         </is>
       </c>
       <c r="E46" t="b">
@@ -4980,20 +5025,20 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bhumika chaudhary</t>
+          <t>Priyanka Verma</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>10/28/1988</t>
+          <t>10/18/1987</t>
         </is>
       </c>
       <c r="E47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -5003,16 +5048,16 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Nimesh</t>
+          <t>Bhumika chaudhary</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>10/30/1987</t>
+          <t>10/28/1988</t>
         </is>
       </c>
       <c r="E48" t="b">
@@ -5022,20 +5067,20 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>November</t>
+          <t>October</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Shobhit kaushik</t>
+          <t>Nimesh</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>11/13/1986</t>
+          <t>10/30/1987</t>
         </is>
       </c>
       <c r="E49" t="b">
@@ -5049,16 +5094,16 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Pratyaksh Tomar</t>
+          <t>Shobhit kaushik</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>11/28/2026</t>
+          <t>11/13/1986</t>
         </is>
       </c>
       <c r="E50" t="b">
@@ -5076,12 +5121,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SUMIT CHHABRA</t>
+          <t>Pratyaksh Tomar</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>11/28/1987</t>
+          <t>11/28/2026</t>
         </is>
       </c>
       <c r="E51" t="b">
@@ -5091,20 +5136,20 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>December</t>
+          <t>November</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ishan Bhardwaj</t>
+          <t>SUMIT CHHABRA</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>12/4/2026</t>
+          <t>11/28/1987</t>
         </is>
       </c>
       <c r="E52" t="b">
@@ -5127,7 +5172,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>12/4/1986</t>
+          <t>12/4/2026</t>
         </is>
       </c>
       <c r="E53" t="b">
@@ -5141,16 +5186,16 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Isha shukla</t>
+          <t>Ishan Bhardwaj</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>12/6/0086</t>
+          <t>12/4/1986</t>
         </is>
       </c>
       <c r="E54" t="b">
@@ -5164,16 +5209,16 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Kriti Sharma</t>
+          <t>Isha shukla</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>12/7/1988</t>
+          <t>12/6/0086</t>
         </is>
       </c>
       <c r="E55" t="b">
@@ -5187,16 +5232,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Shashank Chaudhary</t>
+          <t>Kriti Sharma</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>12/10/1987</t>
+          <t>12/7/1988</t>
         </is>
       </c>
       <c r="E56" t="b">
@@ -5210,16 +5255,16 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Pallavi Sharma</t>
+          <t>Shashank Chaudhary</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>12/14/1989</t>
+          <t>12/10/1987</t>
         </is>
       </c>
       <c r="E57" t="b">
@@ -5233,16 +5278,16 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Gopal Verma</t>
+          <t>Pallavi Sharma</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>12/17/1987</t>
+          <t>12/14/1989</t>
         </is>
       </c>
       <c r="E58" t="b">
@@ -5256,16 +5301,16 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SEERAT KAUR (FORMERLY SUMIT KAPOOR)</t>
+          <t>Gopal Verma</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>12/18/1987</t>
+          <t>12/17/1987</t>
         </is>
       </c>
       <c r="E59" t="b">
@@ -5279,16 +5324,16 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Prasanjeet</t>
+          <t>SEERAT KAUR (FORMERLY SUMIT KAPOOR)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>12/28/1986</t>
+          <t>12/18/1987</t>
         </is>
       </c>
       <c r="E60" t="b">
@@ -5302,25 +5347,48 @@
         </is>
       </c>
       <c r="B61" t="n">
+        <v>28</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Prasanjeet</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>12/28/1986</t>
+        </is>
+      </c>
+      <c r="E61" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>December</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
         <v>29</v>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>Ashu Garg</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>12/29/1986</t>
         </is>
       </c>
-      <c r="E61" t="b">
+      <c r="E62" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E61"/>
-  <conditionalFormatting sqref="A2:E61">
+  <autoFilter ref="A1:E62"/>
+  <conditionalFormatting sqref="A2:E62">
     <cfRule type="expression" priority="1" dxfId="1">
       <formula>$E2=TRUE</formula>
     </cfRule>

--- a/Birthdays.xlsx
+++ b/Birthdays.xlsx
@@ -3581,7 +3581,7 @@
         <v>18</v>
       </c>
       <c r="E47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -5038,7 +5038,7 @@
         </is>
       </c>
       <c r="E47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">

--- a/Birthdays.xlsx
+++ b/Birthdays.xlsx
@@ -3604,7 +3604,7 @@
         <v>28</v>
       </c>
       <c r="E48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="E48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">

--- a/Birthdays.xlsx
+++ b/Birthdays.xlsx
@@ -3604,7 +3604,7 @@
         <v>28</v>
       </c>
       <c r="E48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="E48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">

--- a/Birthdays.xlsx
+++ b/Birthdays.xlsx
@@ -3627,7 +3627,7 @@
         <v>30</v>
       </c>
       <c r="E49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -5084,7 +5084,7 @@
         </is>
       </c>
       <c r="E49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">

--- a/Birthdays.xlsx
+++ b/Birthdays.xlsx
@@ -3627,7 +3627,7 @@
         <v>30</v>
       </c>
       <c r="E49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -5084,7 +5084,7 @@
         </is>
       </c>
       <c r="E49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
